--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ\Data Files\Backoffce\IndexacaoFG\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E34B76CE-1E1E-4516-B5CD-23D707837C43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E91A3F6-99E9-4E98-BB11-C0C2A77C8F65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="13">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -49,6 +49,24 @@
   </si>
   <si>
     <t>Processar</t>
+  </si>
+  <si>
+    <t>133847234</t>
+  </si>
+  <si>
+    <t>971</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa MDS 18.08.2025</t>
+  </si>
+  <si>
+    <t>133873577</t>
+  </si>
+  <si>
+    <t>133906715</t>
+  </si>
+  <si>
+    <t>RECUSAS MDS 18.08.2025</t>
   </si>
 </sst>
 </file>
@@ -444,7 +462,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -475,22 +493,53 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>12</v>
+      </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>12</v>
+      </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>12</v>
+      </c>
       <c r="E4" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="E5" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E91A3F6-99E9-4E98-BB11-C0C2A77C8F65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F265D01F-4DF9-4D12-BFB9-43695BF6CC1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="20">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -51,22 +51,43 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>133847234</t>
-  </si>
-  <si>
     <t>971</t>
   </si>
   <si>
-    <t>Relatório de Recusa MDS 18.08.2025</t>
-  </si>
-  <si>
-    <t>133873577</t>
-  </si>
-  <si>
-    <t>133906715</t>
-  </si>
-  <si>
-    <t>RECUSAS MDS 18.08.2025</t>
+    <t>RECUSAS MDS 19.08.2025</t>
+  </si>
+  <si>
+    <t>133798945</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa MDS 19.08.2025</t>
+  </si>
+  <si>
+    <t>133899469</t>
+  </si>
+  <si>
+    <t>133796652</t>
+  </si>
+  <si>
+    <t>133996688</t>
+  </si>
+  <si>
+    <t>133998120</t>
+  </si>
+  <si>
+    <t>133866087</t>
+  </si>
+  <si>
+    <t>133999224</t>
+  </si>
+  <si>
+    <t>133871543</t>
+  </si>
+  <si>
+    <t>134004063</t>
+  </si>
+  <si>
+    <t>134006382</t>
   </si>
 </sst>
 </file>
@@ -462,7 +483,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -494,16 +515,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -511,16 +532,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -528,18 +549,137 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E4" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F265D01F-4DF9-4D12-BFB9-43695BF6CC1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68824BF9-4ED0-4A37-8BDC-903AFE8ADB29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="12">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,40 +54,16 @@
     <t>971</t>
   </si>
   <si>
-    <t>RECUSAS MDS 19.08.2025</t>
-  </si>
-  <si>
-    <t>133798945</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa MDS 19.08.2025</t>
-  </si>
-  <si>
-    <t>133899469</t>
-  </si>
-  <si>
-    <t>133796652</t>
-  </si>
-  <si>
-    <t>133996688</t>
-  </si>
-  <si>
-    <t>133998120</t>
-  </si>
-  <si>
-    <t>133866087</t>
-  </si>
-  <si>
-    <t>133999224</t>
-  </si>
-  <si>
-    <t>133871543</t>
-  </si>
-  <si>
-    <t>134004063</t>
-  </si>
-  <si>
-    <t>134006382</t>
+    <t>RECUSAS MDS 20.08.2025</t>
+  </si>
+  <si>
+    <t>133821916</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa MDS 20.08.2025</t>
+  </si>
+  <si>
+    <t>133827925</t>
   </si>
 </sst>
 </file>
@@ -483,7 +459,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -547,142 +523,6 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68824BF9-4ED0-4A37-8BDC-903AFE8ADB29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F80553FB-F812-4F36-9885-CBCE83792BA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="14">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,16 +54,22 @@
     <t>971</t>
   </si>
   <si>
-    <t>RECUSAS MDS 20.08.2025</t>
-  </si>
-  <si>
-    <t>133821916</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa MDS 20.08.2025</t>
-  </si>
-  <si>
-    <t>133827925</t>
+    <t>RECUSAS MDS 21.08.2025</t>
+  </si>
+  <si>
+    <t>133941669</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa MDS 21.08.2025</t>
+  </si>
+  <si>
+    <t>133845798</t>
+  </si>
+  <si>
+    <t>133921817</t>
+  </si>
+  <si>
+    <t>133944189</t>
   </si>
 </sst>
 </file>
@@ -459,7 +465,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -523,6 +529,40 @@
         <v>6</v>
       </c>
     </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F80553FB-F812-4F36-9885-CBCE83792BA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED67929D-5989-414F-8014-E741904AB830}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="12">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,22 +54,16 @@
     <t>971</t>
   </si>
   <si>
-    <t>RECUSAS MDS 21.08.2025</t>
-  </si>
-  <si>
-    <t>133941669</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa MDS 21.08.2025</t>
-  </si>
-  <si>
-    <t>133845798</t>
-  </si>
-  <si>
-    <t>133921817</t>
-  </si>
-  <si>
-    <t>133944189</t>
+    <t>RECUSAS MDS 25.08.2025</t>
+  </si>
+  <si>
+    <t>133900631</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa MDS 25.08.2025</t>
+  </si>
+  <si>
+    <t>134003819</t>
   </si>
 </sst>
 </file>
@@ -465,7 +459,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -529,40 +523,6 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED67929D-5989-414F-8014-E741904AB830}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EAAC994-889F-4E10-80DF-520C1C65E888}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1515" yWindow="1515" windowWidth="15375" windowHeight="7875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -54,16 +54,16 @@
     <t>971</t>
   </si>
   <si>
-    <t>RECUSAS MDS 25.08.2025</t>
-  </si>
-  <si>
-    <t>133900631</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa MDS 25.08.2025</t>
-  </si>
-  <si>
-    <t>134003819</t>
+    <t>RECUSAS MDS 26.08.2025</t>
+  </si>
+  <si>
+    <t>134098393</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa MDS 26.08.2025</t>
+  </si>
+  <si>
+    <t>131435324</t>
   </si>
 </sst>
 </file>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EAAC994-889F-4E10-80DF-520C1C65E888}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8ED144EE-2084-4334-9B6D-F753028E5D16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1515" yWindow="1515" windowWidth="15375" windowHeight="7875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3150" yWindow="2955" windowWidth="15375" windowHeight="7875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="13">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,16 +54,19 @@
     <t>971</t>
   </si>
   <si>
-    <t>RECUSAS MDS 26.08.2025</t>
-  </si>
-  <si>
-    <t>134098393</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa MDS 26.08.2025</t>
-  </si>
-  <si>
-    <t>131435324</t>
+    <t>RECUSAS MDS 27.08.2025</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa MDS 27.08.2025</t>
+  </si>
+  <si>
+    <t>134002271</t>
+  </si>
+  <si>
+    <t>134025777</t>
+  </si>
+  <si>
+    <t>134001742</t>
   </si>
 </sst>
 </file>
@@ -459,7 +462,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -491,13 +494,13 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>8</v>
@@ -514,12 +517,29 @@
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E3" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8ED144EE-2084-4334-9B6D-F753028E5D16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82DC53B4-946F-4447-BDF5-E5FA643A9FA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3150" yWindow="2955" windowWidth="15375" windowHeight="7875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="17">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,19 +54,31 @@
     <t>971</t>
   </si>
   <si>
-    <t>RECUSAS MDS 27.08.2025</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa MDS 27.08.2025</t>
-  </si>
-  <si>
-    <t>134002271</t>
-  </si>
-  <si>
-    <t>134025777</t>
-  </si>
-  <si>
-    <t>134001742</t>
+    <t>RECUSAS MDS 28.08.2025</t>
+  </si>
+  <si>
+    <t>133962492</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa MDS 28.08.2025</t>
+  </si>
+  <si>
+    <t>134070825</t>
+  </si>
+  <si>
+    <t>134147384</t>
+  </si>
+  <si>
+    <t>133959620</t>
+  </si>
+  <si>
+    <t>133953036</t>
+  </si>
+  <si>
+    <t>133937338</t>
+  </si>
+  <si>
+    <t>134004176</t>
   </si>
 </sst>
 </file>
@@ -462,7 +474,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -494,13 +506,13 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>8</v>
@@ -517,7 +529,7 @@
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>8</v>
@@ -534,12 +546,80 @@
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E4" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82DC53B4-946F-4447-BDF5-E5FA643A9FA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD099470-5599-4CEA-8D3A-1FC961890CD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="12">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,31 +54,16 @@
     <t>971</t>
   </si>
   <si>
-    <t>RECUSAS MDS 28.08.2025</t>
-  </si>
-  <si>
-    <t>133962492</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa MDS 28.08.2025</t>
-  </si>
-  <si>
-    <t>134070825</t>
-  </si>
-  <si>
-    <t>134147384</t>
-  </si>
-  <si>
-    <t>133959620</t>
-  </si>
-  <si>
-    <t>133953036</t>
-  </si>
-  <si>
-    <t>133937338</t>
-  </si>
-  <si>
-    <t>134004176</t>
+    <t>134151777</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa MDS 29.08.2025</t>
+  </si>
+  <si>
+    <t>134071618</t>
+  </si>
+  <si>
+    <t>RECUSAS MDS 29.08.2025</t>
   </si>
 </sst>
 </file>
@@ -474,7 +459,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -506,16 +491,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -523,103 +508,18 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E8" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD099470-5599-4CEA-8D3A-1FC961890CD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{503E99BB-3353-4787-B3AC-7569960AC5ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="18">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,16 +54,34 @@
     <t>971</t>
   </si>
   <si>
-    <t>134151777</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa MDS 29.08.2025</t>
-  </si>
-  <si>
-    <t>134071618</t>
-  </si>
-  <si>
-    <t>RECUSAS MDS 29.08.2025</t>
+    <t>133980396</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa MDS 01.09.2025</t>
+  </si>
+  <si>
+    <t>134012827</t>
+  </si>
+  <si>
+    <t>134140950</t>
+  </si>
+  <si>
+    <t>134014014</t>
+  </si>
+  <si>
+    <t>134003085</t>
+  </si>
+  <si>
+    <t>134217774</t>
+  </si>
+  <si>
+    <t>134228033</t>
+  </si>
+  <si>
+    <t>134217706</t>
+  </si>
+  <si>
+    <t>RECUSAS MDS 01.09.2025</t>
   </si>
 </sst>
 </file>
@@ -459,7 +477,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -500,7 +518,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -517,9 +535,111 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="B4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{503E99BB-3353-4787-B3AC-7569960AC5ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4919CBE-4BC6-460C-8F83-12A1068B579C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,34 +54,13 @@
     <t>971</t>
   </si>
   <si>
-    <t>133980396</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa MDS 01.09.2025</t>
-  </si>
-  <si>
-    <t>134012827</t>
-  </si>
-  <si>
-    <t>134140950</t>
-  </si>
-  <si>
-    <t>134014014</t>
-  </si>
-  <si>
-    <t>134003085</t>
-  </si>
-  <si>
-    <t>134217774</t>
-  </si>
-  <si>
-    <t>134228033</t>
-  </si>
-  <si>
-    <t>134217706</t>
-  </si>
-  <si>
-    <t>RECUSAS MDS 01.09.2025</t>
+    <t>RECUSAS MDS 02.09.2025</t>
+  </si>
+  <si>
+    <t>134035068</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa MDS 02.09.2025</t>
   </si>
 </sst>
 </file>
@@ -477,7 +456,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -509,137 +488,18 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E9" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4919CBE-4BC6-460C-8F83-12A1068B579C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26AB4206-857E-4C26-BDED-1859CE17568A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="14">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,13 +54,22 @@
     <t>971</t>
   </si>
   <si>
-    <t>RECUSAS MDS 02.09.2025</t>
-  </si>
-  <si>
-    <t>134035068</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa MDS 02.09.2025</t>
+    <t>134217958</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa MDS 03.09.2025</t>
+  </si>
+  <si>
+    <t>134261310</t>
+  </si>
+  <si>
+    <t>134066254</t>
+  </si>
+  <si>
+    <t>134132517</t>
+  </si>
+  <si>
+    <t>RECUSAS MDS 03.09.2025</t>
   </si>
 </sst>
 </file>
@@ -456,7 +465,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -488,18 +497,69 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" s="2" t="s">
+      <c r="B3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26AB4206-857E-4C26-BDED-1859CE17568A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03E9C248-C433-4FCC-8D56-A0BAAA001880}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="18">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,22 +54,34 @@
     <t>971</t>
   </si>
   <si>
-    <t>134217958</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa MDS 03.09.2025</t>
-  </si>
-  <si>
-    <t>134261310</t>
-  </si>
-  <si>
-    <t>134066254</t>
-  </si>
-  <si>
-    <t>134132517</t>
-  </si>
-  <si>
-    <t>RECUSAS MDS 03.09.2025</t>
+    <t>134273785</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa MDS 04.09.2025</t>
+  </si>
+  <si>
+    <t>134259874</t>
+  </si>
+  <si>
+    <t>134274495</t>
+  </si>
+  <si>
+    <t>134077640</t>
+  </si>
+  <si>
+    <t>134122996</t>
+  </si>
+  <si>
+    <t>134291910</t>
+  </si>
+  <si>
+    <t>134204402</t>
+  </si>
+  <si>
+    <t>134108572</t>
+  </si>
+  <si>
+    <t>RECUSAS MDS 04.09.2025</t>
   </si>
 </sst>
 </file>
@@ -465,7 +477,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -506,7 +518,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -523,7 +535,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -540,7 +552,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -557,9 +569,77 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="B6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03E9C248-C433-4FCC-8D56-A0BAAA001880}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{076F9300-C7FE-436C-AB18-0FB2DB754675}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="18">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,34 +54,34 @@
     <t>971</t>
   </si>
   <si>
-    <t>134273785</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa MDS 04.09.2025</t>
-  </si>
-  <si>
-    <t>134259874</t>
-  </si>
-  <si>
-    <t>134274495</t>
-  </si>
-  <si>
-    <t>134077640</t>
-  </si>
-  <si>
-    <t>134122996</t>
-  </si>
-  <si>
-    <t>134291910</t>
-  </si>
-  <si>
-    <t>134204402</t>
-  </si>
-  <si>
-    <t>134108572</t>
-  </si>
-  <si>
-    <t>RECUSAS MDS 04.09.2025</t>
+    <t>134276685</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa MDS 05.09.2025</t>
+  </si>
+  <si>
+    <t>134286838</t>
+  </si>
+  <si>
+    <t>134206399</t>
+  </si>
+  <si>
+    <t>134166656</t>
+  </si>
+  <si>
+    <t>134316804</t>
+  </si>
+  <si>
+    <t>RECUSAS MDS 05.09.2025</t>
+  </si>
+  <si>
+    <t>RECUSAS MDS 06.09.2025</t>
+  </si>
+  <si>
+    <t>134292459</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa MDS 06.09.2025</t>
   </si>
 </sst>
 </file>
@@ -477,7 +477,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -518,7 +518,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -535,7 +535,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -552,7 +552,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -569,7 +569,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -586,7 +586,7 @@
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -594,52 +594,18 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E9" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{076F9300-C7FE-436C-AB18-0FB2DB754675}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4825C2B8-03B8-4C5E-9051-F9515D861808}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4825C2B8-03B8-4C5E-9051-F9515D861808}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5810BF6-3085-4E37-89E7-B3BD22DD3B43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="12">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,34 +54,16 @@
     <t>971</t>
   </si>
   <si>
-    <t>134276685</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa MDS 05.09.2025</t>
-  </si>
-  <si>
-    <t>134286838</t>
-  </si>
-  <si>
-    <t>134206399</t>
-  </si>
-  <si>
-    <t>134166656</t>
-  </si>
-  <si>
-    <t>134316804</t>
-  </si>
-  <si>
-    <t>RECUSAS MDS 05.09.2025</t>
-  </si>
-  <si>
-    <t>RECUSAS MDS 06.09.2025</t>
-  </si>
-  <si>
-    <t>134292459</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa MDS 06.09.2025</t>
+    <t>134319186</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa MDS 08.09.2025</t>
+  </si>
+  <si>
+    <t>134206623</t>
+  </si>
+  <si>
+    <t>RECUSAS MDS 08.09.2025</t>
   </si>
 </sst>
 </file>
@@ -477,7 +459,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -518,7 +500,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -535,77 +517,9 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E7" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5810BF6-3085-4E37-89E7-B3BD22DD3B43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F46BA63-D16C-41E5-9D3B-380FEF83C00E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="16">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,16 +54,28 @@
     <t>971</t>
   </si>
   <si>
-    <t>134319186</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa MDS 08.09.2025</t>
-  </si>
-  <si>
-    <t>134206623</t>
-  </si>
-  <si>
-    <t>RECUSAS MDS 08.09.2025</t>
+    <t>RECUSAS MDS 09.09.2025</t>
+  </si>
+  <si>
+    <t>134254771</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa MDS 09.09.2025</t>
+  </si>
+  <si>
+    <t>134297654</t>
+  </si>
+  <si>
+    <t>134261826</t>
+  </si>
+  <si>
+    <t>134284955</t>
+  </si>
+  <si>
+    <t>134221383</t>
+  </si>
+  <si>
+    <t>134262272</t>
   </si>
 </sst>
 </file>
@@ -459,7 +471,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -491,16 +503,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -508,18 +520,86 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E3" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F46BA63-D16C-41E5-9D3B-380FEF83C00E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA27EB96-5565-4A5C-AC73-BA9DC9C47CB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="26115" yWindow="2220" windowWidth="15375" windowHeight="7875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="15">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,28 +54,25 @@
     <t>971</t>
   </si>
   <si>
-    <t>RECUSAS MDS 09.09.2025</t>
-  </si>
-  <si>
-    <t>134254771</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa MDS 09.09.2025</t>
-  </si>
-  <si>
-    <t>134297654</t>
-  </si>
-  <si>
-    <t>134261826</t>
-  </si>
-  <si>
-    <t>134284955</t>
-  </si>
-  <si>
-    <t>134221383</t>
-  </si>
-  <si>
-    <t>134262272</t>
+    <t>134170658</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa MDS 10.09.2025</t>
+  </si>
+  <si>
+    <t>134297644</t>
+  </si>
+  <si>
+    <t>134313611</t>
+  </si>
+  <si>
+    <t>133921857</t>
+  </si>
+  <si>
+    <t>134273209</t>
+  </si>
+  <si>
+    <t>RECUSAS MDS 10.09.2025</t>
   </si>
 </sst>
 </file>
@@ -471,7 +468,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -503,16 +500,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -520,16 +517,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -537,16 +534,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -554,16 +551,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -571,35 +568,18 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E7" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA27EB96-5565-4A5C-AC73-BA9DC9C47CB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD9FDB64-9DE8-4836-AA0C-AA7F8AE700A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="26115" yWindow="2220" windowWidth="15375" windowHeight="7875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="19">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,25 +54,37 @@
     <t>971</t>
   </si>
   <si>
-    <t>134170658</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa MDS 10.09.2025</t>
-  </si>
-  <si>
-    <t>134297644</t>
-  </si>
-  <si>
-    <t>134313611</t>
-  </si>
-  <si>
-    <t>133921857</t>
-  </si>
-  <si>
-    <t>134273209</t>
-  </si>
-  <si>
-    <t>RECUSAS MDS 10.09.2025</t>
+    <t>134359035</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa MDS 11.09.2025</t>
+  </si>
+  <si>
+    <t>134387035</t>
+  </si>
+  <si>
+    <t>134390499</t>
+  </si>
+  <si>
+    <t>134196568</t>
+  </si>
+  <si>
+    <t>134198781</t>
+  </si>
+  <si>
+    <t>134206193</t>
+  </si>
+  <si>
+    <t>134259166</t>
+  </si>
+  <si>
+    <t>134262839</t>
+  </si>
+  <si>
+    <t>134264898</t>
+  </si>
+  <si>
+    <t>RECUSAS MDS 11.09.2025</t>
   </si>
 </sst>
 </file>
@@ -468,7 +480,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -509,7 +521,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -526,7 +538,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -543,7 +555,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -560,7 +572,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -577,9 +589,77 @@
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="B7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD9FDB64-9DE8-4836-AA0C-AA7F8AE700A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6ECBCC5D-F154-46A5-B774-FDE39172D694}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="18">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,37 +54,34 @@
     <t>971</t>
   </si>
   <si>
-    <t>134359035</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa MDS 11.09.2025</t>
-  </si>
-  <si>
-    <t>134387035</t>
-  </si>
-  <si>
-    <t>134390499</t>
-  </si>
-  <si>
-    <t>134196568</t>
-  </si>
-  <si>
-    <t>134198781</t>
-  </si>
-  <si>
-    <t>134206193</t>
-  </si>
-  <si>
-    <t>134259166</t>
-  </si>
-  <si>
-    <t>134262839</t>
-  </si>
-  <si>
-    <t>134264898</t>
-  </si>
-  <si>
-    <t>RECUSAS MDS 11.09.2025</t>
+    <t>134297501</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa MDS 12.09.2025</t>
+  </si>
+  <si>
+    <t>134308088</t>
+  </si>
+  <si>
+    <t>134398990</t>
+  </si>
+  <si>
+    <t>134271871</t>
+  </si>
+  <si>
+    <t>134284919</t>
+  </si>
+  <si>
+    <t>RECUSAS MDS 12.09.2025</t>
+  </si>
+  <si>
+    <t>131435324</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa MDS 13.09.2025</t>
+  </si>
+  <si>
+    <t>RECUSAS MDS 13.09.2025</t>
   </si>
 </sst>
 </file>
@@ -480,7 +477,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -521,7 +518,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -538,7 +535,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -555,7 +552,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -572,7 +569,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -589,7 +586,7 @@
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -597,69 +594,18 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E10" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6ECBCC5D-F154-46A5-B774-FDE39172D694}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5293EFFF-E9CE-4791-865C-E9166CB0AF01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="16">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,34 +54,28 @@
     <t>971</t>
   </si>
   <si>
-    <t>134297501</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa MDS 12.09.2025</t>
-  </si>
-  <si>
-    <t>134308088</t>
-  </si>
-  <si>
-    <t>134398990</t>
-  </si>
-  <si>
-    <t>134271871</t>
-  </si>
-  <si>
-    <t>134284919</t>
-  </si>
-  <si>
-    <t>RECUSAS MDS 12.09.2025</t>
-  </si>
-  <si>
-    <t>131435324</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa MDS 13.09.2025</t>
-  </si>
-  <si>
-    <t>RECUSAS MDS 13.09.2025</t>
+    <t>RECUSAS MDS 15.09.2025</t>
+  </si>
+  <si>
+    <t>134237323</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa MDS 15.09.2025</t>
+  </si>
+  <si>
+    <t>134405390</t>
+  </si>
+  <si>
+    <t>134339601</t>
+  </si>
+  <si>
+    <t>134311510</t>
+  </si>
+  <si>
+    <t>134313674</t>
+  </si>
+  <si>
+    <t>134314790</t>
   </si>
 </sst>
 </file>
@@ -509,16 +503,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -526,16 +520,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -543,16 +537,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -560,16 +554,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -577,16 +571,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -600,10 +594,10 @@
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5293EFFF-E9CE-4791-865C-E9166CB0AF01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67F157AF-2A35-4396-82D0-32BF8EEB3F16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="17">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,28 +54,31 @@
     <t>971</t>
   </si>
   <si>
-    <t>RECUSAS MDS 15.09.2025</t>
-  </si>
-  <si>
-    <t>134237323</t>
-  </si>
-  <si>
     <t>Relatório de Recusa MDS 15.09.2025</t>
   </si>
   <si>
-    <t>134405390</t>
-  </si>
-  <si>
-    <t>134339601</t>
-  </si>
-  <si>
-    <t>134311510</t>
-  </si>
-  <si>
-    <t>134313674</t>
-  </si>
-  <si>
-    <t>134314790</t>
+    <t>RECUSAS MDS 16.09.2025</t>
+  </si>
+  <si>
+    <t>134345745</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa MDS 16.09.2025</t>
+  </si>
+  <si>
+    <t>134336602</t>
+  </si>
+  <si>
+    <t>134317859</t>
+  </si>
+  <si>
+    <t>134358103</t>
+  </si>
+  <si>
+    <t>134354830</t>
+  </si>
+  <si>
+    <t>134481477</t>
   </si>
 </sst>
 </file>
@@ -503,16 +506,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -520,16 +523,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -537,16 +540,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -554,16 +557,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -571,16 +574,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -588,16 +591,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67F157AF-2A35-4396-82D0-32BF8EEB3F16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B7EB5DC-12FF-44BD-941B-44D110CDAA9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="14">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,31 +54,22 @@
     <t>971</t>
   </si>
   <si>
-    <t>Relatório de Recusa MDS 15.09.2025</t>
-  </si>
-  <si>
-    <t>RECUSAS MDS 16.09.2025</t>
-  </si>
-  <si>
-    <t>134345745</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa MDS 16.09.2025</t>
-  </si>
-  <si>
-    <t>134336602</t>
-  </si>
-  <si>
-    <t>134317859</t>
-  </si>
-  <si>
-    <t>134358103</t>
-  </si>
-  <si>
-    <t>134354830</t>
-  </si>
-  <si>
-    <t>134481477</t>
+    <t>RECUSAS MDS 17.09.2025</t>
+  </si>
+  <si>
+    <t>134361299</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa MDS 17.09.2025</t>
+  </si>
+  <si>
+    <t>134447574</t>
+  </si>
+  <si>
+    <t>134287790</t>
+  </si>
+  <si>
+    <t>134489042</t>
   </si>
 </sst>
 </file>
@@ -474,7 +465,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -506,16 +497,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -523,16 +514,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>8</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>9</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -540,16 +531,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>8</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>9</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -557,52 +548,18 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>9</v>
-      </c>
       <c r="E5" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E7" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B7EB5DC-12FF-44BD-941B-44D110CDAA9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00F0DC9B-3CFC-47A2-8D1A-95C7500C539F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -54,22 +54,22 @@
     <t>971</t>
   </si>
   <si>
-    <t>RECUSAS MDS 17.09.2025</t>
-  </si>
-  <si>
-    <t>134361299</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa MDS 17.09.2025</t>
-  </si>
-  <si>
-    <t>134447574</t>
-  </si>
-  <si>
-    <t>134287790</t>
-  </si>
-  <si>
-    <t>134489042</t>
+    <t>RECUSAS MDS 18.09.2025</t>
+  </si>
+  <si>
+    <t>134384760</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa MDS 18.09.2025</t>
+  </si>
+  <si>
+    <t>134379757</t>
+  </si>
+  <si>
+    <t>134317529</t>
+  </si>
+  <si>
+    <t>134434529</t>
   </si>
 </sst>
 </file>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00F0DC9B-3CFC-47A2-8D1A-95C7500C539F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92064E57-805F-4170-A617-524ED1E5DB8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="15">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,22 +54,25 @@
     <t>971</t>
   </si>
   <si>
-    <t>RECUSAS MDS 18.09.2025</t>
-  </si>
-  <si>
-    <t>134384760</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa MDS 18.09.2025</t>
-  </si>
-  <si>
-    <t>134379757</t>
-  </si>
-  <si>
-    <t>134317529</t>
-  </si>
-  <si>
-    <t>134434529</t>
+    <t>134420870</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa MDS 19.09.2025</t>
+  </si>
+  <si>
+    <t>134555285</t>
+  </si>
+  <si>
+    <t>RECUSAS MDS 19.09.2025</t>
+  </si>
+  <si>
+    <t>RECUSAS MDS 21.09.2025</t>
+  </si>
+  <si>
+    <t>888209387</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa MDS 21.09.2025</t>
   </si>
 </sst>
 </file>
@@ -465,7 +468,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -497,16 +500,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -514,16 +517,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -531,35 +534,18 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E5" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92064E57-805F-4170-A617-524ED1E5DB8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01426DB7-CC08-4B86-8EC9-C5702D6CC31E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="15">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,25 +54,25 @@
     <t>971</t>
   </si>
   <si>
-    <t>134420870</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa MDS 19.09.2025</t>
-  </si>
-  <si>
-    <t>134555285</t>
-  </si>
-  <si>
-    <t>RECUSAS MDS 19.09.2025</t>
-  </si>
-  <si>
-    <t>RECUSAS MDS 21.09.2025</t>
-  </si>
-  <si>
-    <t>888209387</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa MDS 21.09.2025</t>
+    <t>RECUSAS MDS 22.09.2025</t>
+  </si>
+  <si>
+    <t>134529277</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa MDS 22.09.2025</t>
+  </si>
+  <si>
+    <t>131089027</t>
+  </si>
+  <si>
+    <t>134408772</t>
+  </si>
+  <si>
+    <t>134570277</t>
+  </si>
+  <si>
+    <t>134577540</t>
   </si>
 </sst>
 </file>
@@ -468,7 +468,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -500,16 +500,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -517,16 +517,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -534,18 +534,52 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" s="2" t="s">
+      <c r="B6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01426DB7-CC08-4B86-8EC9-C5702D6CC31E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E904757-1C22-4E9A-AAAE-7FFE7E4210D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="13">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,25 +54,19 @@
     <t>971</t>
   </si>
   <si>
-    <t>RECUSAS MDS 22.09.2025</t>
-  </si>
-  <si>
-    <t>134529277</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa MDS 22.09.2025</t>
-  </si>
-  <si>
-    <t>131089027</t>
-  </si>
-  <si>
-    <t>134408772</t>
-  </si>
-  <si>
-    <t>134570277</t>
-  </si>
-  <si>
-    <t>134577540</t>
+    <t>RECUSAS MDS 23.09.2025</t>
+  </si>
+  <si>
+    <t>134382195</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa MDS 23.09.2025</t>
+  </si>
+  <si>
+    <t>134424461</t>
+  </si>
+  <si>
+    <t>134594859</t>
   </si>
 </sst>
 </file>
@@ -468,7 +462,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -549,40 +543,6 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E904757-1C22-4E9A-AAAE-7FFE7E4210D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3127F036-0665-4FF1-BC51-91497AEE7031}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -54,19 +54,19 @@
     <t>971</t>
   </si>
   <si>
-    <t>RECUSAS MDS 23.09.2025</t>
-  </si>
-  <si>
-    <t>134382195</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa MDS 23.09.2025</t>
-  </si>
-  <si>
-    <t>134424461</t>
-  </si>
-  <si>
-    <t>134594859</t>
+    <t>RECUSAS MDS 24.09.2025</t>
+  </si>
+  <si>
+    <t>134495821</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa MDS 24.09.2025</t>
+  </si>
+  <si>
+    <t>134404436</t>
+  </si>
+  <si>
+    <t>134477781</t>
   </si>
 </sst>
 </file>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3127F036-0665-4FF1-BC51-91497AEE7031}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4BE9E20-E9F1-4E58-926D-71A831F59983}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -54,19 +54,19 @@
     <t>971</t>
   </si>
   <si>
-    <t>RECUSAS MDS 24.09.2025</t>
-  </si>
-  <si>
-    <t>134495821</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa MDS 24.09.2025</t>
-  </si>
-  <si>
-    <t>134404436</t>
-  </si>
-  <si>
-    <t>134477781</t>
+    <t>RECUSAS MDS 06.10.2025</t>
+  </si>
+  <si>
+    <t>134659141</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa MDS 06.10.2025</t>
+  </si>
+  <si>
+    <t>134805541</t>
+  </si>
+  <si>
+    <t>134661621</t>
   </si>
 </sst>
 </file>
@@ -557,31 +557,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4BE9E20-E9F1-4E58-926D-71A831F59983}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2A47D06-6571-4ECE-A651-9059B461B45A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -51,13 +51,13 @@
     <t>Processar</t>
   </si>
   <si>
+    <t>RECUSAS MDS 06.10.2025</t>
+  </si>
+  <si>
+    <t>134659141</t>
+  </si>
+  <si>
     <t>971</t>
-  </si>
-  <si>
-    <t>RECUSAS MDS 06.10.2025</t>
-  </si>
-  <si>
-    <t>134659141</t>
   </si>
   <si>
     <t>Relatório de Recusa MDS 06.10.2025</t>
@@ -494,16 +494,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -514,13 +514,13 @@
         <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -531,13 +531,13 @@
         <v>12</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2A47D06-6571-4ECE-A651-9059B461B45A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B9C7945-C707-4916-B679-6D27F26A9805}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -51,22 +51,22 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>RECUSAS MDS 06.10.2025</t>
-  </si>
-  <si>
-    <t>134659141</t>
-  </si>
-  <si>
     <t>971</t>
   </si>
   <si>
-    <t>Relatório de Recusa MDS 06.10.2025</t>
-  </si>
-  <si>
-    <t>134805541</t>
-  </si>
-  <si>
-    <t>134661621</t>
+    <t>134813717</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa MDS 08.10.2025</t>
+  </si>
+  <si>
+    <t>888210565</t>
+  </si>
+  <si>
+    <t>134833970</t>
+  </si>
+  <si>
+    <t>RECUSAS MDS 08.10.2025</t>
   </si>
 </sst>
 </file>
@@ -497,13 +497,13 @@
         <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>10</v>
-      </c>
       <c r="D2" s="2" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -511,16 +511,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>10</v>
-      </c>
       <c r="D3" s="2" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -528,16 +528,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>12</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>7</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -557,31 +557,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B9C7945-C707-4916-B679-6D27F26A9805}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C047FDA-FBFB-4440-BE8D-C05BE8C5CC13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="24">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,19 +54,52 @@
     <t>971</t>
   </si>
   <si>
-    <t>134813717</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa MDS 08.10.2025</t>
-  </si>
-  <si>
-    <t>888210565</t>
-  </si>
-  <si>
-    <t>134833970</t>
-  </si>
-  <si>
-    <t>RECUSAS MDS 08.10.2025</t>
+    <t>134654465</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa MDS 09.10.2025</t>
+  </si>
+  <si>
+    <t>134734765</t>
+  </si>
+  <si>
+    <t>134761158</t>
+  </si>
+  <si>
+    <t>134730432</t>
+  </si>
+  <si>
+    <t>134785359</t>
+  </si>
+  <si>
+    <t>134819214</t>
+  </si>
+  <si>
+    <t>134827229</t>
+  </si>
+  <si>
+    <t>134824956</t>
+  </si>
+  <si>
+    <t>888210854</t>
+  </si>
+  <si>
+    <t>888210924</t>
+  </si>
+  <si>
+    <t>134689505</t>
+  </si>
+  <si>
+    <t>131089027</t>
+  </si>
+  <si>
+    <t>133158694</t>
+  </si>
+  <si>
+    <t>134730093</t>
+  </si>
+  <si>
+    <t>RECUSAS MDS 09.10.2025</t>
   </si>
 </sst>
 </file>
@@ -462,7 +495,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -503,7 +536,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -520,7 +553,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -537,9 +570,196 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="B5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -557,31 +777,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C047FDA-FBFB-4440-BE8D-C05BE8C5CC13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5013078-D116-4745-B0AA-05EA2C0BE15D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="13">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,52 +54,19 @@
     <t>971</t>
   </si>
   <si>
-    <t>134654465</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa MDS 09.10.2025</t>
-  </si>
-  <si>
-    <t>134734765</t>
-  </si>
-  <si>
-    <t>134761158</t>
-  </si>
-  <si>
-    <t>134730432</t>
-  </si>
-  <si>
-    <t>134785359</t>
-  </si>
-  <si>
-    <t>134819214</t>
-  </si>
-  <si>
-    <t>134827229</t>
-  </si>
-  <si>
-    <t>134824956</t>
-  </si>
-  <si>
-    <t>888210854</t>
-  </si>
-  <si>
-    <t>888210924</t>
-  </si>
-  <si>
-    <t>134689505</t>
-  </si>
-  <si>
-    <t>131089027</t>
-  </si>
-  <si>
-    <t>133158694</t>
-  </si>
-  <si>
-    <t>134730093</t>
-  </si>
-  <si>
-    <t>RECUSAS MDS 09.10.2025</t>
+    <t>134865878</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa MDS 10.10.2025</t>
+  </si>
+  <si>
+    <t>134680804</t>
+  </si>
+  <si>
+    <t>133933177</t>
+  </si>
+  <si>
+    <t>RECUSAS MDS 10.10.2025</t>
   </si>
 </sst>
 </file>
@@ -495,7 +462,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -536,7 +503,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -553,7 +520,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -570,196 +537,9 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E15" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -777,31 +557,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5013078-D116-4745-B0AA-05EA2C0BE15D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC64913B-6079-4DCB-BFF7-A9CED38A8E25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="27">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,19 +54,61 @@
     <t>971</t>
   </si>
   <si>
-    <t>134865878</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa MDS 10.10.2025</t>
-  </si>
-  <si>
-    <t>134680804</t>
-  </si>
-  <si>
-    <t>133933177</t>
-  </si>
-  <si>
-    <t>RECUSAS MDS 10.10.2025</t>
+    <t>134922907</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa MDS 16.10.2025</t>
+  </si>
+  <si>
+    <t>134922151</t>
+  </si>
+  <si>
+    <t>134965327</t>
+  </si>
+  <si>
+    <t>RECUSAS MDS 16.10.2025</t>
+  </si>
+  <si>
+    <t>134803447</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa MDS 14.10.2025</t>
+  </si>
+  <si>
+    <t>134924167</t>
+  </si>
+  <si>
+    <t>888211282</t>
+  </si>
+  <si>
+    <t>132583487</t>
+  </si>
+  <si>
+    <t>134923140</t>
+  </si>
+  <si>
+    <t>134794808</t>
+  </si>
+  <si>
+    <t>RECUSAS MDS 14.10.2025</t>
+  </si>
+  <si>
+    <t>134890632</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa MDS 15.10.2025</t>
+  </si>
+  <si>
+    <t>131058291</t>
+  </si>
+  <si>
+    <t>134948293</t>
+  </si>
+  <si>
+    <t>132777967</t>
+  </si>
+  <si>
+    <t>RECUSAS MDS 15.10.2025</t>
   </si>
 </sst>
 </file>
@@ -462,7 +504,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -543,6 +585,176 @@
         <v>6</v>
       </c>
     </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -557,31 +769,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC64913B-6079-4DCB-BFF7-A9CED38A8E25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F58D1192-2618-41C3-B04D-533737860174}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="18">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,61 +54,34 @@
     <t>971</t>
   </si>
   <si>
-    <t>134922907</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa MDS 16.10.2025</t>
-  </si>
-  <si>
-    <t>134922151</t>
-  </si>
-  <si>
-    <t>134965327</t>
-  </si>
-  <si>
-    <t>RECUSAS MDS 16.10.2025</t>
-  </si>
-  <si>
-    <t>134803447</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa MDS 14.10.2025</t>
-  </si>
-  <si>
-    <t>134924167</t>
-  </si>
-  <si>
-    <t>888211282</t>
-  </si>
-  <si>
-    <t>132583487</t>
-  </si>
-  <si>
-    <t>134923140</t>
-  </si>
-  <si>
-    <t>134794808</t>
-  </si>
-  <si>
-    <t>RECUSAS MDS 14.10.2025</t>
-  </si>
-  <si>
-    <t>134890632</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa MDS 15.10.2025</t>
-  </si>
-  <si>
-    <t>131058291</t>
-  </si>
-  <si>
-    <t>134948293</t>
-  </si>
-  <si>
-    <t>132777967</t>
-  </si>
-  <si>
-    <t>RECUSAS MDS 15.10.2025</t>
+    <t>134838787</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa MDS 17.10.2025</t>
+  </si>
+  <si>
+    <t>134845415</t>
+  </si>
+  <si>
+    <t>134818791</t>
+  </si>
+  <si>
+    <t>134943534</t>
+  </si>
+  <si>
+    <t>134959144</t>
+  </si>
+  <si>
+    <t>134859550</t>
+  </si>
+  <si>
+    <t>134859970</t>
+  </si>
+  <si>
+    <t>134825341</t>
+  </si>
+  <si>
+    <t>RECUSAS MDS 17.10.2025</t>
   </si>
 </sst>
 </file>
@@ -504,7 +477,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -545,7 +518,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -562,7 +535,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -579,7 +552,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -587,16 +560,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -604,16 +577,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -621,16 +594,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -638,16 +611,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -655,103 +628,18 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E14" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -769,31 +657,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F58D1192-2618-41C3-B04D-533737860174}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{000D1EAF-D5BC-48BB-865D-698E71A612CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="13">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,34 +54,19 @@
     <t>971</t>
   </si>
   <si>
-    <t>134838787</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa MDS 17.10.2025</t>
-  </si>
-  <si>
-    <t>134845415</t>
-  </si>
-  <si>
-    <t>134818791</t>
-  </si>
-  <si>
-    <t>134943534</t>
-  </si>
-  <si>
-    <t>134959144</t>
-  </si>
-  <si>
-    <t>134859550</t>
-  </si>
-  <si>
-    <t>134859970</t>
-  </si>
-  <si>
-    <t>134825341</t>
-  </si>
-  <si>
-    <t>RECUSAS MDS 17.10.2025</t>
+    <t>134826339</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa MDS 21.10.2025</t>
+  </si>
+  <si>
+    <t>134446200</t>
+  </si>
+  <si>
+    <t>134882798</t>
+  </si>
+  <si>
+    <t>RECUSAS MDS 21.10.2025</t>
   </si>
 </sst>
 </file>
@@ -477,7 +462,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -518,7 +503,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -535,7 +520,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -552,94 +537,9 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E9" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -657,31 +557,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{000D1EAF-D5BC-48BB-865D-698E71A612CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9203D0B-B89C-4007-B031-7517A7AF923A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="12">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,19 +54,16 @@
     <t>971</t>
   </si>
   <si>
-    <t>134826339</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa MDS 21.10.2025</t>
-  </si>
-  <si>
-    <t>134446200</t>
-  </si>
-  <si>
-    <t>134882798</t>
-  </si>
-  <si>
-    <t>RECUSAS MDS 21.10.2025</t>
+    <t>135010642</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa MDS 22.10.2025</t>
+  </si>
+  <si>
+    <t>135049898</t>
+  </si>
+  <si>
+    <t>RECUSAS MDS 22.10.2025</t>
   </si>
 </sst>
 </file>
@@ -462,7 +459,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -503,7 +500,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -520,26 +517,9 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -557,31 +537,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9203D0B-B89C-4007-B031-7517A7AF923A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{651A2678-D3FE-45CA-B3FF-2AFB6EA8F8B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="690" yWindow="1665" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="16">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,16 +54,28 @@
     <t>971</t>
   </si>
   <si>
-    <t>135010642</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa MDS 22.10.2025</t>
-  </si>
-  <si>
-    <t>135049898</t>
-  </si>
-  <si>
-    <t>RECUSAS MDS 22.10.2025</t>
+    <t>130751818</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa MDS 23.10.2025</t>
+  </si>
+  <si>
+    <t>134885397</t>
+  </si>
+  <si>
+    <t>134992149</t>
+  </si>
+  <si>
+    <t>135070685</t>
+  </si>
+  <si>
+    <t>135069745</t>
+  </si>
+  <si>
+    <t>135081499</t>
+  </si>
+  <si>
+    <t>RECUSAS MDS 23.10.2025</t>
   </si>
 </sst>
 </file>
@@ -459,7 +471,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -500,7 +512,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -517,9 +529,77 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="B4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -537,31 +617,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{651A2678-D3FE-45CA-B3FF-2AFB6EA8F8B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{494B2C01-EBA4-4D68-836E-EF090FC6CC13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="690" yWindow="1665" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -54,28 +54,28 @@
     <t>971</t>
   </si>
   <si>
-    <t>130751818</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa MDS 23.10.2025</t>
-  </si>
-  <si>
-    <t>134885397</t>
-  </si>
-  <si>
-    <t>134992149</t>
-  </si>
-  <si>
-    <t>135070685</t>
-  </si>
-  <si>
-    <t>135069745</t>
-  </si>
-  <si>
-    <t>135081499</t>
-  </si>
-  <si>
-    <t>RECUSAS MDS 23.10.2025</t>
+    <t>135048971</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa MDS 24.10.2025</t>
+  </si>
+  <si>
+    <t>135085703</t>
+  </si>
+  <si>
+    <t>135096078</t>
+  </si>
+  <si>
+    <t>133753806</t>
+  </si>
+  <si>
+    <t>RECUSAS MDS 24.10.2025</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa MDS 25.10.2025</t>
+  </si>
+  <si>
+    <t>RECUSAS MDS 25.10.2025</t>
   </si>
 </sst>
 </file>
@@ -512,7 +512,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -529,7 +529,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -546,7 +546,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -563,7 +563,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -571,13 +571,13 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>15</v>
@@ -588,13 +588,13 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>15</v>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{494B2C01-EBA4-4D68-836E-EF090FC6CC13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBEEC7C7-6A0F-495D-84E3-E5FE3A2F0A4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="14">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,28 +54,22 @@
     <t>971</t>
   </si>
   <si>
-    <t>135048971</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa MDS 24.10.2025</t>
-  </si>
-  <si>
-    <t>135085703</t>
-  </si>
-  <si>
-    <t>135096078</t>
-  </si>
-  <si>
-    <t>133753806</t>
-  </si>
-  <si>
-    <t>RECUSAS MDS 24.10.2025</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa MDS 25.10.2025</t>
-  </si>
-  <si>
-    <t>RECUSAS MDS 25.10.2025</t>
+    <t>RECUSAS MDS 27.10.2025</t>
+  </si>
+  <si>
+    <t>135080039</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa MDS 27.10.2025</t>
+  </si>
+  <si>
+    <t>135084357</t>
+  </si>
+  <si>
+    <t>135099547</t>
+  </si>
+  <si>
+    <t>134998500</t>
   </si>
 </sst>
 </file>
@@ -471,7 +465,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -503,16 +497,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -520,16 +514,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -537,16 +531,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -554,52 +548,18 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E7" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -617,31 +577,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D61CBFA-07DF-4FF0-BA4A-592D7C9C835F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D334D3E1-799A-4B9E-AE69-5E5BFFD7F6E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="12">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,31 +54,16 @@
     <t>971</t>
   </si>
   <si>
-    <t>134575898</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa MDS 03.10.2025</t>
-  </si>
-  <si>
-    <t>134637863</t>
-  </si>
-  <si>
-    <t>134637664</t>
-  </si>
-  <si>
-    <t>134685202</t>
-  </si>
-  <si>
-    <t>134758448</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa MDS 04.10.2025</t>
-  </si>
-  <si>
-    <t>RECUSAS MDS 03.10.2025</t>
-  </si>
-  <si>
-    <t>RECUSAS MDS 04.10.2025</t>
+    <t>135853527</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa MDS 18.12.2025</t>
+  </si>
+  <si>
+    <t>135734008</t>
+  </si>
+  <si>
+    <t>RECUSA MDS 18.12.2025</t>
   </si>
 </sst>
 </file>
@@ -474,7 +459,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -515,7 +500,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -533,60 +518,9 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E6" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -604,31 +538,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D334D3E1-799A-4B9E-AE69-5E5BFFD7F6E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr documentId="13_ncr:1_{60CB2D7D-2548-4ECA-9DDA-61DBB8E2CC02}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowHeight="11040" windowWidth="20730" xWindow="-120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}" yWindow="-120"/>
   </bookViews>
   <sheets>
-    <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
+    <sheet name="IndexacaoFG" r:id="rId1" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">IndexacaoFG!$A$1:$F$1</definedName>
+    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">IndexacaoFG!$A$1:$F$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
   </extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="15">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,22 +54,32 @@
     <t>971</t>
   </si>
   <si>
-    <t>135853527</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa MDS 18.12.2025</t>
-  </si>
-  <si>
-    <t>135734008</t>
-  </si>
-  <si>
-    <t>RECUSA MDS 18.12.2025</t>
+    <t>140929140</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa MDS 01.10.2026</t>
+  </si>
+  <si>
+    <t>141122913</t>
+  </si>
+  <si>
+    <t>141169402</t>
+  </si>
+  <si>
+    <t>RECUSA MDS 01.10.2026</t>
+  </si>
+  <si>
+    <t>Processado</t>
+  </si>
+  <si>
+    <t>&lt;u&gt;Documentos indexados&lt;/u&gt;:1-&gt; RECUSA MDS 01.10.2026.xlsx.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -123,31 +133,31 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
   <cellXfs count="6">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
+    <xf applyAlignment="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="49" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1" borderId="0" fillId="2" fontId="1" numFmtId="49" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf applyAlignment="1" applyFill="1" applyFont="1" borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf applyAlignment="1" applyFill="1" applyFont="1" borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle builtinId="0" name="Normal" xfId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -164,10 +174,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:sysClr lastClr="000000" val="windowText"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr lastClr="FFFFFF" val="window"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -202,7 +212,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin panose="020F0302020204030204" typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -254,7 +264,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin panose="020F0502020204030204" typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -365,21 +375,21 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cap="flat" cmpd="sng" w="6350">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cap="flat" cmpd="sng" w="12700">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cap="flat" cmpd="sng" w="19050">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -396,7 +406,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw algn="ctr" blurRad="57150" dir="5400000" dist="19050" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -448,25 +458,25 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" name="Office Theme" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="4" width="49.5703125" style="2" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="16.42578125" style="2" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="84.7109375" style="2" customWidth="1" collapsed="1"/>
-    <col min="7" max="16384" width="9.140625" style="2" collapsed="1"/>
+    <col min="1" max="2" customWidth="true" style="1" width="16.7109375" collapsed="true"/>
+    <col min="3" max="4" customWidth="true" style="2" width="49.5703125" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="2" width="16.42578125" collapsed="true"/>
+    <col min="6" max="6" customWidth="true" style="2" width="84.7109375" collapsed="true"/>
+    <col min="7" max="16384" style="2" width="9.140625" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -500,12 +510,14 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F2"/>
+        <v>13</v>
+      </c>
+      <c r="F2" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
@@ -518,51 +530,74 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>6</v>
+      <c r="B4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.51181102362204722" right="0.51181102362204722" top="0.78740157480314965" bottom="0.78740157480314965" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageMargins bottom="0.78740157480314965" footer="0.31496062992125984" header="0.31496062992125984" left="0.51181102362204722" right="0.51181102362204722" top="0.78740157480314965"/>
+  <pageSetup orientation="portrait" paperSize="9" r:id="rId1"/>
   <headerFooter>
-    <oddFooter>&amp;L&amp;"Calibri,Regular"&amp;08&amp;B&amp;K7F7F7FClassificação Allianz:&amp;K595959 &amp;K7F7F7FINTERNO</oddFooter>
-    <evenFooter>&amp;L&amp;"Calibri,Regular"&amp;08&amp;B&amp;K7F7F7FClassificação Allianz:&amp;K595959 &amp;K7F7F7FINTERNO</evenFooter>
-    <firstFooter>&amp;L&amp;"Calibri,Regular"&amp;08&amp;B&amp;K7F7F7FClassificação Allianz:&amp;K595959 &amp;K7F7F7FINTERNO</firstFooter>
+    <oddFooter><![CDATA[&L&"Calibri,Regular"&08&B&K7F7F7FClassificação Allianz:&K595959 &K7F7F7FINTERNO]]></oddFooter>
+    <evenFooter><![CDATA[&L&"Calibri,Regular"&08&B&K7F7F7FClassificação Allianz:&K595959 &K7F7F7FINTERNO]]></evenFooter>
+    <firstFooter><![CDATA[&L&"Calibri,Regular"&08&B&K7F7F7FClassificação Allianz:&K595959 &K7F7F7FINTERNO]]></firstFooter>
   </headerFooter>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>